--- a/artfynd/A 43101-2023 artfynd.xlsx
+++ b/artfynd/A 43101-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123301150</v>
       </c>
       <c r="B2" t="n">
-        <v>79355</v>
+        <v>79358</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>123301161</v>
       </c>
       <c r="B3" t="n">
-        <v>90952</v>
+        <v>90955</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 43101-2023 artfynd.xlsx
+++ b/artfynd/A 43101-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123301150</v>
       </c>
       <c r="B2" t="n">
-        <v>79358</v>
+        <v>79360</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>123301161</v>
       </c>
       <c r="B3" t="n">
-        <v>90955</v>
+        <v>90957</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 43101-2023 artfynd.xlsx
+++ b/artfynd/A 43101-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123301150</v>
+        <v>123301161</v>
       </c>
       <c r="B2" t="n">
-        <v>79360</v>
+        <v>90963</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Koriseberget, Ång</t>
+          <t>N Asketjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>617173</v>
+        <v>617252</v>
       </c>
       <c r="R2" t="n">
-        <v>6975117</v>
+        <v>6974966</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>739</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,7 +785,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Måns Svensson</t>
+          <t>Linnéa Kjellberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123301161</v>
+        <v>123301150</v>
       </c>
       <c r="B3" t="n">
-        <v>90957</v>
+        <v>79361</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,34 +812,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>N Asketjärnsberget, Ång</t>
+          <t>Koriseberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>617252</v>
+        <v>617173</v>
       </c>
       <c r="R3" t="n">
-        <v>6974966</v>
+        <v>6975117</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>739</t>
+          <t>750</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,7 +906,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Linnéa Kjellberg</t>
+          <t>Måns Svensson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 43101-2023 artfynd.xlsx
+++ b/artfynd/A 43101-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123301161</v>
       </c>
       <c r="B2" t="n">
-        <v>90963</v>
+        <v>90966</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>123301150</v>
       </c>
       <c r="B3" t="n">
-        <v>79361</v>
+        <v>79364</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 43101-2023 artfynd.xlsx
+++ b/artfynd/A 43101-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123301161</v>
       </c>
       <c r="B2" t="n">
-        <v>90966</v>
+        <v>90983</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>123301150</v>
       </c>
       <c r="B3" t="n">
-        <v>79364</v>
+        <v>79370</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 43101-2023 artfynd.xlsx
+++ b/artfynd/A 43101-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123301161</v>
+        <v>123301150</v>
       </c>
       <c r="B2" t="n">
-        <v>90983</v>
+        <v>79375</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>229821</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>N Asketjärnsberget, Ång</t>
+          <t>Koriseberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>617252</v>
+        <v>617173</v>
       </c>
       <c r="R2" t="n">
-        <v>6974966</v>
+        <v>6975117</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>739</t>
+          <t>750</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,7 +785,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Linnéa Kjellberg</t>
+          <t>Måns Svensson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123301150</v>
+        <v>123301161</v>
       </c>
       <c r="B3" t="n">
-        <v>79370</v>
+        <v>90988</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,34 +812,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Koriseberget, Ång</t>
+          <t>N Asketjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>617173</v>
+        <v>617252</v>
       </c>
       <c r="R3" t="n">
-        <v>6975117</v>
+        <v>6974966</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>739</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,7 +906,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Måns Svensson</t>
+          <t>Linnéa Kjellberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 43101-2023 artfynd.xlsx
+++ b/artfynd/A 43101-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123301150</v>
       </c>
       <c r="B2" t="n">
-        <v>79375</v>
+        <v>79377</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>123301161</v>
       </c>
       <c r="B3" t="n">
-        <v>90988</v>
+        <v>90990</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 43101-2023 artfynd.xlsx
+++ b/artfynd/A 43101-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123301150</v>
+        <v>123301161</v>
       </c>
       <c r="B2" t="n">
-        <v>79377</v>
+        <v>90990</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Koriseberget, Ång</t>
+          <t>N Asketjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>617173</v>
+        <v>617252</v>
       </c>
       <c r="R2" t="n">
-        <v>6975117</v>
+        <v>6974966</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>739</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,7 +785,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Måns Svensson</t>
+          <t>Linnéa Kjellberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123301161</v>
+        <v>123301150</v>
       </c>
       <c r="B3" t="n">
-        <v>90990</v>
+        <v>79377</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,34 +812,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>N Asketjärnsberget, Ång</t>
+          <t>Koriseberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>617252</v>
+        <v>617173</v>
       </c>
       <c r="R3" t="n">
-        <v>6974966</v>
+        <v>6975117</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>739</t>
+          <t>750</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,7 +906,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Linnéa Kjellberg</t>
+          <t>Måns Svensson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 43101-2023 artfynd.xlsx
+++ b/artfynd/A 43101-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123301161</v>
+        <v>123301150</v>
       </c>
       <c r="B2" t="n">
-        <v>90990</v>
+        <v>79377</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>229821</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>N Asketjärnsberget, Ång</t>
+          <t>Koriseberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>617252</v>
+        <v>617173</v>
       </c>
       <c r="R2" t="n">
-        <v>6974966</v>
+        <v>6975117</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>739</t>
+          <t>750</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,7 +785,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Linnéa Kjellberg</t>
+          <t>Måns Svensson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123301150</v>
+        <v>123301161</v>
       </c>
       <c r="B3" t="n">
-        <v>79377</v>
+        <v>90990</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,34 +812,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Koriseberget, Ång</t>
+          <t>N Asketjärnsberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>617173</v>
+        <v>617252</v>
       </c>
       <c r="R3" t="n">
-        <v>6975117</v>
+        <v>6974966</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>739</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,7 +906,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Måns Svensson</t>
+          <t>Linnéa Kjellberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 43101-2023 artfynd.xlsx
+++ b/artfynd/A 43101-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123301161</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -918,6 +928,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123301162</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1034,8 +1049,18 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123301150</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>